--- a/BMA_Entities_CRUD.xlsx
+++ b/BMA_Entities_CRUD.xlsx
@@ -2444,7 +2444,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>no, date, index (01 | 02), subject, file_url</t>
+          <t>no, date, index (general_01 | student_02), subject, eflow, e_sign, p_sign, file_url</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">

--- a/BMA_Entities_CRUD.xlsx
+++ b/BMA_Entities_CRUD.xlsx
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>resource (26), op (c|r|u|d), allowed</t>
+          <t>resource (23), op (c|r|u|d), allowed</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>no, date, index (general_01 | student_02), subject, eflow, e_sign, p_sign, file_url</t>
+          <t>no, date, subject, eflow, e_sign, p_sign, file_url</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>ბრძანება მხოლოდ აიტვირთება და იკითხება — სისტემაში სხვა ჩანაწერს არ ებმევა, არაფრის წინაპირობა არ არის</t>
+          <t>რეგისტრში ქვეყნდება მხოლოდ ზოგადი ბრძანებები; მხოლოდ აიტვირთება და იკითხება — სისტემაში სხვა ჩანაწერს არ ებმევა, არაფრის წინაპირობა არ არის</t>
         </is>
       </c>
     </row>

--- a/BMA_Entities_CRUD.xlsx
+++ b/BMA_Entities_CRUD.xlsx
@@ -2444,7 +2444,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>no, date, subject, eflow, e_sign, p_sign, file_url</t>
+          <t>no, date, subject, eflow, amends_order_no, file_url</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
